--- a/Results/Consensus/CC/CC_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
+++ b/Results/Consensus/CC/CC_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
@@ -4464,7 +4464,7 @@
         <v>282</v>
       </c>
       <c r="B280" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="281">
